--- a/signup_forms/003_happy_hour_waitlist_sign_up--signup_forms.xlsx
+++ b/signup_forms/003_happy_hour_waitlist_sign_up--signup_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,13 +538,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reservation_time</t>
+          <t>Reservation Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>reservation_date</t>
+          <t>Reservation Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reservation_note</t>
+          <t>Reservation Note</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>number_of_guests</t>
+          <t>Number of Guests</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>special_request</t>
+          <t>Special Request</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -781,17 +781,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reservation_time</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>reservation_time</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -804,17 +804,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reservation_date</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>reservation_date</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -827,251 +827,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>reservation_note</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>reservation_note</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>special_request</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>special_request</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reservation_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>reservation_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>reservation_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>reservation_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>reservation_note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>reservation_note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>special_request</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>special_request</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
